--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_validation.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_validation.xlsx
@@ -587,31 +587,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8910053086246883</v>
+        <v>0.7536078466345479</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9963129840206002</v>
+        <v>0.99064824750947</v>
       </c>
       <c r="K2" t="n">
         <v>48</v>
@@ -620,16 +620,16 @@
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -638,19 +638,19 @@
         <v>11</v>
       </c>
       <c r="S2" t="n">
-        <v>5.81855420565098e-05</v>
+        <v>4.654843364520784e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00107061397383978</v>
+        <v>0.000861146022436345</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02127659574468085</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06382978723404255</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06382978723404255</v>
+        <v>0</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -684,31 +684,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9811320754716981</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9005685649885059</v>
+        <v>0.7900841350594088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9966616326132506</v>
+        <v>0.9922835330378734</v>
       </c>
       <c r="K3" t="n">
         <v>48</v>
@@ -717,16 +717,16 @@
         <v>9</v>
       </c>
       <c r="M3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="Q3" t="n">
         <v>0.8888888888888888</v>
@@ -738,16 +738,16 @@
         <v>9.309686729041568e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001908485779453521</v>
+        <v>0.001885211562630917</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01923076923076923</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="W3" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.333333333333333</v>
+        <v>2.888888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -781,70 +781,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9803921568627451</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8969519232441061</v>
+        <v>0.7820151050048196</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9965303967465577</v>
+        <v>0.9919307806988522</v>
       </c>
       <c r="K4" t="n">
         <v>53</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002199413489736071</v>
+        <v>0.002071405297211749</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002478704091607318</v>
+        <v>0.00279290601871247</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.714285714285714</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
@@ -878,31 +878,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9795918367346939</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8930623153224584</v>
+        <v>0.7820151050048196</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9963884204614692</v>
+        <v>0.9919307806988522</v>
       </c>
       <c r="K5" t="n">
         <v>53</v>
@@ -911,37 +911,37 @@
         <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1714285714285714</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003339850114043663</v>
+        <v>0.002595075175720337</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002164502164502165</v>
+        <v>0.001419727226178839</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>3.142857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -1116,34 +1116,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5958436145024278</v>
+        <v>0.3755282641185388</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9821242504842788</v>
+        <v>0.9637768390302125</v>
       </c>
       <c r="L2" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -1173,13 +1173,13 @@
         <v>0.002117953730856957</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1194,28 +1194,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5655085052479191</v>
+        <v>0.2065432914738929</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -1266,28 +1266,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7411599827511859</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -1317,10 +1317,10 @@
         <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0003258390355164549</v>
+        <v>0.0001629195177582274</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008960573476702509</v>
+        <v>0.006028022157054416</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1344,28 +1344,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6456611570247934</v>
+        <v>0.3423719528896192</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -1398,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1494,28 +1494,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7411599827511859</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4384939195509823</v>
+        <v>0.3423719528896192</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1626,10 +1626,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1644,34 +1644,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5958436145024278</v>
+        <v>0.3755282641185388</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9821242504842788</v>
+        <v>0.9637768390302125</v>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1701,13 +1701,13 @@
         <v>0.001792114695340502</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1722,28 +1722,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5655085052479191</v>
+        <v>0.2065432914738929</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1794,28 +1794,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7411599827511859</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -1827,16 +1827,16 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.125</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.125</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0.0001629195177582274</v>
       </c>
       <c r="U11" t="n">
-        <v>0.009286412512218964</v>
+        <v>0.007168458781362007</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1872,28 +1872,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6456611570247934</v>
+        <v>0.3423719528896192</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>226.5</v>
+        <v>224</v>
       </c>
       <c r="M13" t="n">
         <v>5</v>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7574992425007574</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -2055,16 +2055,16 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -2076,7 +2076,7 @@
         <v>0.0001629195177582274</v>
       </c>
       <c r="U14" t="n">
-        <v>0.001792114695340502</v>
+        <v>0.003584229390681004</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2100,34 +2100,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5100999795960008</v>
+        <v>0.4384939195509823</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -2160,10 +2160,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2178,52 +2178,52 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5649937852319399</v>
+        <v>0.3755282641185388</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9801096286728695</v>
+        <v>0.9637768390302125</v>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2232,7 +2232,7 @@
         <v>0.003910068426197458</v>
       </c>
       <c r="U16" t="n">
-        <v>0.003421309872922776</v>
+        <v>0.001466275659824047</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2256,28 +2256,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5655085052479191</v>
+        <v>0.2065432914738929</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -2328,28 +2328,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7411599827511859</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -2361,28 +2361,28 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>0.005050505050505051</v>
+        <v>0.006679700228087325</v>
       </c>
       <c r="U18" t="n">
-        <v>0.007168458781362007</v>
+        <v>0.01971326164874552</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2406,28 +2406,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6456611570247934</v>
+        <v>0.3423719528896192</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2505,34 +2505,34 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01221896383186706</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01955034213098729</v>
+        <v>0.01319648093841642</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2556,28 +2556,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7574992425007574</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -2604,22 +2604,22 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>0.005702183121537961</v>
+        <v>0.004398826979472141</v>
       </c>
       <c r="U21" t="n">
-        <v>0.002932551319648094</v>
+        <v>0.003095470837406321</v>
       </c>
       <c r="V21" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2634,34 +2634,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4</v>
-      </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5100999795960008</v>
+        <v>0.4384939195509823</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
@@ -2694,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2712,52 +2712,52 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5649937852319399</v>
+        <v>0.3755282641185388</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9801096286728695</v>
+        <v>0.9637768390302125</v>
       </c>
       <c r="L23" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>6</v>
@@ -2766,7 +2766,7 @@
         <v>0.003910068426197458</v>
       </c>
       <c r="U23" t="n">
-        <v>0.001955034213098729</v>
+        <v>0.0009775171065493646</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2790,28 +2790,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5655085052479191</v>
+        <v>0.2065432914738929</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -2862,28 +2862,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7224598312333834</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -2895,16 +2895,16 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6875</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0625</v>
+        <v>0.1</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2913,10 +2913,10 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>0.01678071032909743</v>
+        <v>0.008471814923427827</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01466275659824047</v>
+        <v>0.008471814923427827</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2940,28 +2940,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6456611570247934</v>
+        <v>0.3423719528896192</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -2991,13 +2991,13 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3021,10 +3021,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>3</v>
@@ -3039,43 +3039,43 @@
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>0.01270772238514174</v>
+        <v>0.01564027370478983</v>
       </c>
       <c r="U27" t="n">
-        <v>0.008960573476702509</v>
+        <v>0.007168458781362007</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -3090,28 +3090,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7411599827511859</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -3123,28 +3123,28 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T28" t="n">
-        <v>0.009449332029977192</v>
+        <v>0.004398826979472141</v>
       </c>
       <c r="U28" t="n">
-        <v>0.003584229390681004</v>
+        <v>0.002117953730856957</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3168,34 +3168,34 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
         <v>3</v>
       </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4</v>
-      </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5100999795960008</v>
+        <v>0.4384939195509823</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
@@ -3228,10 +3228,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16746,7 +16746,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_validation.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_validation.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -835,7 +835,7 @@
         <v>0.002071405297211749</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00279290601871247</v>
+        <v>0.002862728669180282</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2505,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M20" t="n">
         <v>2</v>
@@ -2532,7 +2532,7 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01319648093841642</v>
+        <v>0.01417399804496579</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16746,7 +16746,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_validation.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_validation.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16746,7 +16746,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
